--- a/basedatos_partidas/salida/descompuestos/05.04.01.220.xlsx
+++ b/basedatos_partidas/salida/descompuestos/05.04.01.220.xlsx
@@ -584,10 +584,10 @@
         <v>0.25</v>
       </c>
       <c r="G11" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="12">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>28.5</v>
+        <v>28.55</v>
       </c>
     </row>
     <row r="13">
@@ -743,7 +743,7 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>37.37</v>
+        <v>37.42</v>
       </c>
       <c r="H21" t="n">
         <v>0.37</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="G22" s="4" t="n"/>
       <c r="H22" s="5" t="n">
-        <v>37.74</v>
+        <v>37.79</v>
       </c>
     </row>
   </sheetData>
